--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501719</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501724</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136501726</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136501729</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136501730</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136501720</v>
       </c>
       <c r="B8" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136501727</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136501728</v>
       </c>
       <c r="B10" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501719</v>
       </c>
       <c r="B3" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501724</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136501726</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136501729</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136501730</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136501720</v>
       </c>
       <c r="B8" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501719</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501724</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136501726</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136501729</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136501730</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136501720</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501719</v>
       </c>
       <c r="B3" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501724</v>
       </c>
       <c r="B4" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136501726</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136501729</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136501730</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136501720</v>
       </c>
       <c r="B8" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136501719</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136501724</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136501726</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136501729</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136501730</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136501720</v>
       </c>
       <c r="B8" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37152-2026 artfynd.xlsx
+++ b/artfynd/A 37152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136501721</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136501718</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>136501723</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
